--- a/config/string_config.xlsx
+++ b/config/string_config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12860"/>
+    <workbookView windowHeight="23960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1304,7 +1304,7 @@
     <t>TID_SORT_GAME_CATEGORY_WORD_BREEDS</t>
   </si>
   <si>
-    <t>Breeds</t>
+    <t>Cats</t>
   </si>
   <si>
     <t>TID_SORT_GAME_CATEGORY_WORD_LANDMARK</t>
@@ -4142,13 +4142,13 @@
     <t>TID_SORT_GAME_BASIC_WORD_KENNEDY</t>
   </si>
   <si>
-    <t>Kennedy</t>
+    <t>Washington</t>
   </si>
   <si>
     <t>TID_SORT_GAME_BASIC_WORD_CLINTON</t>
   </si>
   <si>
-    <t>Clinton</t>
+    <t>Jefferson</t>
   </si>
   <si>
     <t>TID_SORT_GAME_BASIC_WORD_LINCOLN</t>
@@ -4160,19 +4160,19 @@
     <t>TID_SORT_GAME_BASIC_WORD_REAGAN</t>
   </si>
   <si>
-    <t>Reagan</t>
+    <t>Roosevelt</t>
   </si>
   <si>
     <t>TID_SORT_GAME_BASIC_WORD_BUSH</t>
   </si>
   <si>
-    <t>Bush</t>
+    <t>Wilson</t>
   </si>
   <si>
     <t>TID_SORT_GAME_BASIC_WORD_OBAMA</t>
   </si>
   <si>
-    <t>Obama</t>
+    <t>Jackson</t>
   </si>
   <si>
     <t>TID_SORT_GAME_BASIC_WORD_ADAMS</t>
@@ -4184,7 +4184,7 @@
     <t>TID_SORT_GAME_BASIC_WORD_BIDEN</t>
   </si>
   <si>
-    <t>Biden</t>
+    <t>Madison</t>
   </si>
   <si>
     <t>TID_SORT_GAME_BASIC_WORD_SOFT_BUN</t>
@@ -6545,19 +6545,19 @@
     <t>TID_SORT_GAME_BASIC_WORD_SYBARITE</t>
   </si>
   <si>
-    <t>Sybarite</t>
+    <t>Cuisine</t>
   </si>
   <si>
     <t>TID_SORT_GAME_BASIC_WORD_HEDONISM</t>
   </si>
   <si>
-    <t>Hedonism</t>
+    <t>Savory</t>
   </si>
   <si>
     <t>TID_SORT_GAME_BASIC_WORD_DISHES</t>
   </si>
   <si>
-    <t>Dishes</t>
+    <t>Delicacy</t>
   </si>
   <si>
     <t>TID_SORT_GAME_BASIC_WORD_ROLE</t>
@@ -10621,7 +10621,7 @@
         <v>424</v>
       </c>
       <c r="B214" s="4"/>
-      <c r="C214" s="3" t="s">
+      <c r="C214" s="6" t="s">
         <v>425</v>
       </c>
     </row>
@@ -14941,7 +14941,7 @@
         <v>1370</v>
       </c>
       <c r="B694" s="4"/>
-      <c r="C694" s="3" t="s">
+      <c r="C694" s="6" t="s">
         <v>1371</v>
       </c>
     </row>
@@ -14950,7 +14950,7 @@
         <v>1372</v>
       </c>
       <c r="B695" s="4"/>
-      <c r="C695" s="3" t="s">
+      <c r="C695" s="6" t="s">
         <v>1373</v>
       </c>
     </row>
@@ -14968,7 +14968,7 @@
         <v>1376</v>
       </c>
       <c r="B697" s="4"/>
-      <c r="C697" s="3" t="s">
+      <c r="C697" s="6" t="s">
         <v>1377</v>
       </c>
     </row>
@@ -14977,7 +14977,7 @@
         <v>1378</v>
       </c>
       <c r="B698" s="4"/>
-      <c r="C698" s="3" t="s">
+      <c r="C698" s="6" t="s">
         <v>1379</v>
       </c>
     </row>
@@ -14986,7 +14986,7 @@
         <v>1380</v>
       </c>
       <c r="B699" s="4"/>
-      <c r="C699" s="3" t="s">
+      <c r="C699" s="6" t="s">
         <v>1381</v>
       </c>
     </row>
@@ -15004,7 +15004,7 @@
         <v>1384</v>
       </c>
       <c r="B701" s="4"/>
-      <c r="C701" s="3" t="s">
+      <c r="C701" s="6" t="s">
         <v>1385</v>
       </c>
     </row>
@@ -18577,7 +18577,7 @@
         <v>2171</v>
       </c>
       <c r="B1098" s="4"/>
-      <c r="C1098" s="3" t="s">
+      <c r="C1098" s="6" t="s">
         <v>2172</v>
       </c>
     </row>
@@ -18586,7 +18586,7 @@
         <v>2173</v>
       </c>
       <c r="B1099" s="4"/>
-      <c r="C1099" s="3" t="s">
+      <c r="C1099" s="6" t="s">
         <v>2174</v>
       </c>
     </row>
@@ -18595,7 +18595,7 @@
         <v>2175</v>
       </c>
       <c r="B1100" s="4"/>
-      <c r="C1100" s="5" t="s">
+      <c r="C1100" s="6" t="s">
         <v>2176</v>
       </c>
     </row>
